--- a/output/pdf_financials_xlsx/MPCT.UN.xlsx
+++ b/output/pdf_financials_xlsx/MPCT.UN.xlsx
@@ -801,40 +801,40 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>4.878</v>
+        <v>5.449</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6.95</v>
+        <v>28.737</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>56.036</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>68.408</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>62.32</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>46.672</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>26.054</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>29.041</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>32.816</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>32.344</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>30.966</v>
       </c>
     </row>
     <row r="11">
@@ -1925,22 +1925,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.378</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>80.157</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>20.764</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>11.757</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>60.927</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>46.73</v>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
@@ -1948,19 +1948,19 @@
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>8.430999999999999</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.244</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.244</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>16.217</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>5.369</v>
       </c>
     </row>
     <row r="35">
@@ -2015,22 +2015,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.378</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>80.157</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>20.764</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>11.757</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>60.927</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>46.73</v>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
@@ -2038,19 +2038,19 @@
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>8.430999999999999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>2.244</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>2.244</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>16.217</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>5.369</v>
       </c>
     </row>
     <row r="37">
@@ -2555,22 +2555,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>31.807</v>
+        <v>29.429</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>214.474</v>
+        <v>134.317</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.015</v>
+        <v>116.351</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.891</v>
+        <v>111.739</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>8.904999999999999</v>
+        <v>110.454</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>4.434</v>
+        <v>103.109</v>
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
@@ -2578,19 +2578,19 @@
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>3.891</v>
+        <v>9.837999999999999</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.944</v>
+        <v>9.01</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>3.944</v>
+        <v>9.01</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.475</v>
+        <v>3.695</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.096</v>
+        <v>0.623</v>
       </c>
     </row>
     <row r="49">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -9390,7 +9390,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -39422,7 +39422,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -39562,7 +39562,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E444" s="5" t="n">
@@ -39572,16 +39572,16 @@
         <v>28.737</v>
       </c>
       <c r="G444" s="5" t="n">
-        <v>-56.036</v>
+        <v>56.036</v>
       </c>
       <c r="H444" s="5" t="n">
-        <v>-68.408</v>
+        <v>68.408</v>
       </c>
       <c r="I444" s="5" t="n">
-        <v>-62.32</v>
+        <v>62.32</v>
       </c>
       <c r="J444" s="5" t="n">
-        <v>-46.672</v>
+        <v>46.672</v>
       </c>
       <c r="K444" t="inlineStr">
         <is>
@@ -39589,19 +39589,19 @@
         </is>
       </c>
       <c r="L444" s="5" t="n">
-        <v>-26.054</v>
+        <v>26.054</v>
       </c>
       <c r="M444" s="5" t="n">
-        <v>-29.041</v>
+        <v>29.041</v>
       </c>
       <c r="N444" s="5" t="n">
-        <v>-32.816</v>
+        <v>32.816</v>
       </c>
       <c r="O444" s="5" t="n">
-        <v>-32.344</v>
+        <v>32.344</v>
       </c>
       <c r="P444" s="5" t="n">
-        <v>-30.966</v>
+        <v>30.966</v>
       </c>
     </row>
     <row r="445">
@@ -40934,7 +40934,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
@@ -46690,7 +46690,7 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
@@ -50446,7 +50446,7 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
@@ -51408,7 +51408,7 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">

--- a/output/pdf_financials_xlsx/MPCT.UN.xlsx
+++ b/output/pdf_financials_xlsx/MPCT.UN.xlsx
@@ -1071,28 +1071,28 @@
         <v>-15.185</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-4.388</v>
+        <v>-24.028</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>13.902</v>
+        <v>24.423</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>32.331</v>
+        <v>67.395</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>21.45</v>
+        <v>41.699</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-43.554</v>
+        <v>-89.551</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-44.145</v>
+        <v>-102.823</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-26.033</v>
+        <v>-61.989</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-54.045</v>
+        <v>-108.677</v>
       </c>
     </row>
     <row r="17">
@@ -1114,28 +1114,28 @@
         <v>1.821</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-5.084</v>
+        <v>14.556</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-10.521</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>-35.064</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-20.249</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>45.997</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.001</v>
+        <v>58.679</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0</v>
+        <v>35.956</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>54.632</v>
       </c>
     </row>
     <row r="18">
@@ -1337,10 +1337,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0</v>
+        <v>3.568</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0</v>
+        <v>3.037</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>0</v>
@@ -1664,28 +1664,28 @@
         <v>-15.185</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-4.388</v>
+        <v>-24.028</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>13.902</v>
+        <v>24.423</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>32.331</v>
+        <v>67.395</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>21.45</v>
+        <v>41.699</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-43.554</v>
+        <v>-89.551</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-44.145</v>
+        <v>-102.823</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-26.033</v>
+        <v>-61.989</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-54.045</v>
+        <v>-108.677</v>
       </c>
     </row>
     <row r="28">
@@ -1750,28 +1750,28 @@
         <v>-11.485</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.042</v>
+        <v>-17.598</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>20.623</v>
+        <v>31.144</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>32.331</v>
+        <v>67.395</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>21.924</v>
+        <v>42.173</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-41.885</v>
+        <v>-87.88200000000001</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-42.54</v>
+        <v>-101.218</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-23.909</v>
+        <v>-59.865</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-52.227</v>
+        <v>-106.859</v>
       </c>
     </row>
     <row r="30">
@@ -1793,22 +1793,22 @@
         <v>-11.60628568541256</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.024109946093241</v>
+        <v>-26.06184467744802</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>52.50922978994272</v>
+        <v>79.29726288987906</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>59.37304881184119</v>
+        <v>123.7650126712454</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>79.45205479452055</v>
+        <v>152.8339494092919</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-154.6427912128484</v>
+        <v>-324.4674173896991</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-775.287042099508</v>
+        <v>-1844.687443047203</v>
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
@@ -1840,28 +1840,28 @@
         <v>-11.99209746460323</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-115.8614402917046</v>
+        <v>-60.57932412185784</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>43.07824591573517</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>52.02759848653461</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>48.55991750401688</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0</v>
+        <v>-51.36402720237629</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0.002265262204100125</v>
+        <v>-57.06797117376462</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0</v>
+        <v>-58.00383939085967</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0</v>
+        <v>-50.27006634338452</v>
       </c>
     </row>
     <row r="32">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>40.885</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -26036,7 +26036,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -37536,7 +37540,11 @@
           <t>Proceeds from the sale of marketable securities, net</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E417" s="5" t="n">
         <v>40.885</v>
       </c>
@@ -39988,7 +39996,11 @@
           <t>LOSS BEFORE INCOME TAX RECOVERY</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
           <t>-</t>
@@ -40058,7 +40070,11 @@
           <t>Deferred income tax recovery 21</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
           <t>-</t>
@@ -40126,7 +40142,11 @@
           <t>TOTAL INCOME TAX RECOVERY</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E452" t="inlineStr">
         <is>
           <t>-</t>
@@ -41468,7 +41488,11 @@
           <t>Deferred income tax recovery 20</t>
         </is>
       </c>
-      <c r="D470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E470" t="inlineStr">
         <is>
           <t>-</t>
@@ -41542,7 +41566,11 @@
           <t>TOTAL INCOME TAX RECOVERY</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E471" t="inlineStr">
         <is>
           <t>-</t>
@@ -43060,7 +43088,11 @@
           <t>EARNINGS (LOSS) BEFORE INCOME TAX RECOVERY</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr">
         <is>
           <t>-</t>
@@ -43134,7 +43166,11 @@
           <t>Current income tax recovery 21</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr">
         <is>
           <t>-</t>
@@ -44010,7 +44046,11 @@
           <t>EARNINGS BEFORE INCOME TAX RECOVERY (EXPENSE) 27,120 6,011</t>
         </is>
       </c>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
           <t>-</t>
@@ -44084,7 +44124,11 @@
           <t>Current income tax recovery 1,469 18</t>
         </is>
       </c>
-      <c r="D506" t="inlineStr"/>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E506" t="inlineStr">
         <is>
           <t>-</t>
@@ -45066,7 +45110,11 @@
           <t>Net income from discontinued operations 4,354</t>
         </is>
       </c>
-      <c r="D519" t="inlineStr"/>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E519" t="inlineStr">
         <is>
           <t>-</t>
@@ -46990,7 +47038,11 @@
           <t>EARNINGS (LOSS) BEFORE INCOME TAX RECOVERY (EXPENSE)</t>
         </is>
       </c>
-      <c r="D545" t="inlineStr"/>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E545" t="inlineStr">
         <is>
           <t>-</t>
@@ -47064,7 +47116,11 @@
           <t>Current income tax recovery (expense) 25</t>
         </is>
       </c>
-      <c r="D546" t="inlineStr"/>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E546" t="inlineStr">
         <is>
           <t>-</t>
@@ -47138,7 +47194,11 @@
           <t>Deferred income tax recovery (expense) 25</t>
         </is>
       </c>
-      <c r="D547" t="inlineStr"/>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E547" t="inlineStr">
         <is>
           <t>-</t>
@@ -47212,7 +47272,11 @@
           <t>TOTAL INCOME TAX RECOVERY (EXPENSE)</t>
         </is>
       </c>
-      <c r="D548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E548" t="inlineStr">
         <is>
           <t>-</t>
@@ -50668,7 +50732,11 @@
           <t>Current income tax recovery (expense) 24</t>
         </is>
       </c>
-      <c r="D595" t="inlineStr"/>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E595" t="inlineStr">
         <is>
           <t>-</t>
@@ -50742,7 +50810,11 @@
           <t>Deferred income tax recovery (expense) 24</t>
         </is>
       </c>
-      <c r="D596" t="inlineStr"/>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E596" t="inlineStr">
         <is>
           <t>-</t>
@@ -51862,7 +51934,11 @@
           <t>Current income tax recovery (expense) 23</t>
         </is>
       </c>
-      <c r="D611" t="inlineStr"/>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E611" t="inlineStr">
         <is>
           <t>-</t>
